--- a/artfynd/A 47695-2023 artfynd.xlsx
+++ b/artfynd/A 47695-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47695-2023 artfynd.xlsx
+++ b/artfynd/A 47695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1174128</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585658.2932106471</v>
+        <v>585658</v>
       </c>
       <c r="R2" t="n">
-        <v>6619404.132289695</v>
+        <v>6619404</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2012-03-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-03-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,6 +787,574 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>61379209</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenbrobacke (SV om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>585572</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6619418</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-09-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-09-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vet inte om död eller levande. Blixt stilla i vägkant, såg hel och fräsch ut, men stel. Kanske börjar bli segt för dessa...</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>59966283</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenbrobacke (SV delen), Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>585552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619459</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-06-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-06-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ett mindre bestånd</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>54487925</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenbrobacke (SV om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585663</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619383</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Större bestrånd i dike vid T--vägkorsningen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>60292938</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Böle by (åkerholme SO om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>585494</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87489721</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenbro backe, SV om, trevägskorsningen (gullklöver), Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>585663</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619384</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>U-Väs-1040</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>större bestånd i dike vid T-vägskorsning</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>dike</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47695-2023 artfynd.xlsx
+++ b/artfynd/A 47695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1174128</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59966283</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54487925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60292938</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,8 +1385,21 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87489721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>